--- a/app/pipeline_output/werize/mapping_werize_Origination.xlsx
+++ b/app/pipeline_output/werize/mapping_werize_Origination.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Mapping'!$A$1:$I$144</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'For Review'!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'For Review'!$A$1:$I$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -822,7 +822,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Age is a core demographic attribute of the applicant.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Standard applicant demographic data.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME2</t>
+          <t>DOCUMENTNAME1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.1.document</t>
+          <t>loanAccount.loanDocuments.0.document</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
@@ -1147,47 +1147,47 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>bankStatement1Password</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER1</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.1.value</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.1.value</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>llm_parameter_bucket</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Relates to accessing an applicant's personal bank statement document.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1204,17 +1204,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID3</t>
+          <t>DOCUMENTID2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.2.documentId</t>
+          <t>loanAccount.loanDocuments.1.documentId</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
@@ -1249,17 +1249,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME4</t>
+          <t>DOCUMENTNAME2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.3.document</t>
+          <t>loanAccount.loanDocuments.1.document</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
@@ -1282,47 +1282,47 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>bankStatement2Password</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER2</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.2.value</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM3</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.2.value</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>llm_parameter_bucket</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Relates to accessing an applicant's personal bank statement document.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID5</t>
+          <t>DOCUMENTID3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.4.documentId</t>
+          <t>loanAccount.loanDocuments.2.documentId</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME6</t>
+          <t>DOCUMENTNAME3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.5.document</t>
+          <t>loanAccount.loanDocuments.2.document</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
@@ -1417,47 +1417,47 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>bankStatement3Password</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER3</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.3.value</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM4</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.3.value</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>llm_parameter_bucket</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Relates to accessing an applicant's personal bank statement document.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1474,17 +1474,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID7</t>
+          <t>DOCUMENTID4</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.6.documentId</t>
+          <t>loanAccount.loanDocuments.3.documentId</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME8</t>
+          <t>DOCUMENTNAME4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.7.document</t>
+          <t>loanAccount.loanDocuments.3.document</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
@@ -1552,47 +1552,47 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>bankStatement4Password</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER4</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.4.value</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.4.value</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>llm_parameter_bucket</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Relates to accessing an applicant's personal bank statement document.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1609,17 +1609,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID9</t>
+          <t>DOCUMENTID5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.8.documentId</t>
+          <t>loanAccount.loanDocuments.4.documentId</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME10</t>
+          <t>DOCUMENTNAME5</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.9.document</t>
+          <t>loanAccount.loanDocuments.4.document</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
@@ -1687,47 +1687,47 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>bankStatement5Password</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER5</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.5.value</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM6</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.5.value</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>llm_parameter_bucket</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Relates to accessing an applicant's personal bank statement document.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID11</t>
+          <t>DOCUMENTID6</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.10.documentId</t>
+          <t>loanAccount.loanDocuments.5.documentId</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
@@ -1789,17 +1789,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME12</t>
+          <t>DOCUMENTNAME6</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.11.document</t>
+          <t>loanAccount.loanDocuments.5.document</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
@@ -1822,47 +1822,47 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>bankStatement6Password</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER6</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.6.value</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM7</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.6.value</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>llm_parameter_bucket</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Relates to accessing an applicant's personal bank statement document.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1879,17 +1879,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID13</t>
+          <t>DOCUMENTID7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.12.documentId</t>
+          <t>loanAccount.loanDocuments.6.documentId</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
@@ -1924,17 +1924,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME14</t>
+          <t>DOCUMENTNAME7</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.13.document</t>
+          <t>loanAccount.loanDocuments.6.document</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
@@ -1957,47 +1957,47 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>bankStatement7Password</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER7</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.7.value</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM8</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.7.value</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>llm_parameter_bucket</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Relates to accessing an applicant's personal bank statement document.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2014,17 +2014,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME15</t>
+          <t>DOCUMENTNAME8</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.14.document</t>
+          <t>loanAccount.loanDocuments.7.document</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID16</t>
+          <t>DOCUMENTID8</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.15.documentId</t>
+          <t>loanAccount.loanDocuments.7.documentId</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID17</t>
+          <t>DOCUMENTID9</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.16.documentId</t>
+          <t>loanAccount.loanDocuments.8.documentId</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID18</t>
+          <t>DOCUMENTID10</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.17.documentId</t>
+          <t>loanAccount.loanDocuments.9.documentId</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
@@ -2194,17 +2194,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME19</t>
+          <t>DOCUMENTNAME9</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.18.document</t>
+          <t>loanAccount.loanDocuments.8.document</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
@@ -2329,17 +2329,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME20</t>
+          <t>DOCUMENTNAME10</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.19.document</t>
+          <t>loanAccount.loanDocuments.9.document</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER8</t>
+          <t>LOANPARAMETER1</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.8.value</t>
+          <t>loanAccount.loanParameters.1.value</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is an identifier for the credit bureau check performed for this specific loan application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Refers to a specific credit bureau enquiry ID generated for the loan application.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM2</t>
+          <t>LOANAPPLICANTPARAM9</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.1.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.8.value</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field represents a component of the applicant's current residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Part of the applicant's personal residence address.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM3</t>
+          <t>LOANAPPLICANTPARAM10</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.2.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.9.value</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field represents a component of the applicant's current residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Part of the applicant's personal residence address.</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM4</t>
+          <t>LOANAPPLICANTPARAM11</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.3.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.10.value</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field represents a component of the applicant's current residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Part of the applicant's personal residence address.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2869,17 +2869,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER9</t>
+          <t>LOANPARAMETER2</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.9.value</t>
+          <t>loanAccount.loanParameters.2.value</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This field represents the status message from a deduplication check, which is an application-level process.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a system status message related to the loan origination process.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2914,17 +2914,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER10</t>
+          <t>LOANPARAMETER3</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.10.value</t>
+          <t>loanAccount.loanParameters.3.value</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This field represents the status message from a deduplication check, which is an application-level process.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a system status message related to the loan origination process.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM5</t>
+          <t>LOANAPPLICANTPARAM12</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.4.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.11.value</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field describes the applicant's employment address, which is part of their profile.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes the applicant's place of employment, a key part of their profile.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM6</t>
+          <t>LOANAPPLICANTPARAM13</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.5.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.12.value</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field identifies the applicant's employer, which is part of their employment profile.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes the applicant's employer name, a key part of their profile.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER11</t>
+          <t>LOANPARAMETER4</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.11.value</t>
+          <t>loanAccount.loanParameters.4.value</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. FOIR (Fixed Obligations to Income Ratio) is a key underwriting metric calculated for the loan application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A key calculated underwriting parameter (Fixed Obligation to Income Ratio) for loan eligibility.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3499,17 +3499,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER12</t>
+          <t>LOANPARAMETER5</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.12.value</t>
+          <t>loanAccount.loanParameters.5.value</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This field defines the start date for interest calculation, a fundamental term of the loan.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific term of the loan product, related to repayment structure.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3634,17 +3634,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID21</t>
+          <t>DOCUMENTID11</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.20.documentId</t>
+          <t>loanAccount.loanDocuments.10.documentId</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
@@ -3679,17 +3679,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME22</t>
+          <t>DOCUMENTNAME11</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.21.document</t>
+          <t>loanAccount.loanDocuments.10.document</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME23</t>
+          <t>DOCUMENTNAME12</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.22.document</t>
+          <t>loanAccount.loanDocuments.11.document</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3994,17 +3994,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER13</t>
+          <t>LOANPARAMETER6</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.13.value</t>
+          <t>loanAccount.loanParameters.6.value</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a reference identifier from a deduplication check, which is an application-level process.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. An identifier generated during the application's deduplication process.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER14</t>
+          <t>LOANPARAMETER7</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.14.value</t>
+          <t>loanAccount.loanParameters.7.value</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This field represents the loan's tenure, a fundamental parameter of the loan structure.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Defines the loan tenure, a fundamental loan term.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4489,17 +4489,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID24</t>
+          <t>DOCUMENTID12</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.23.documentId</t>
+          <t>loanAccount.loanDocuments.11.documentId</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
@@ -4534,17 +4534,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME25</t>
+          <t>DOCUMENTNAME13</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.24.document</t>
+          <t>loanAccount.loanDocuments.12.document</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
@@ -4579,17 +4579,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID26</t>
+          <t>DOCUMENTID13</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.25.documentId</t>
+          <t>loanAccount.loanDocuments.12.documentId</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME27</t>
+          <t>DOCUMENTNAME14</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.26.document</t>
+          <t>loanAccount.loanDocuments.13.document</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM7</t>
+          <t>LOANAPPLICANTPARAM14</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.6.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.13.value</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field represents a component of the applicant's permanent residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Part of the applicant's personal permanent address.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM8</t>
+          <t>LOANAPPLICANTPARAM15</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.7.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field represents a component of the applicant's permanent residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Part of the applicant's personal permanent address.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM9</t>
+          <t>LOANAPPLICANTPARAM16</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.8.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.15.value</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field represents a component of the applicant's permanent residential address.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Part of the applicant's personal permanent address.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM10</t>
+          <t>LOANAPPLICANTPARAM17</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.9.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.16.value</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This describes the applicant's living situation (e.g., owned, rented), a personal profile attribute.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes the applicant's personal living situation at their current address.</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM11</t>
+          <t>LOANAPPLICANTPARAM18</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.10.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.17.value</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This describes the applicant's living situation (e.g., owned, rented) at their permanent address, a personal profile attribute.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes the applicant's personal living situation at their permanent address.</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5344,17 +5344,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID28</t>
+          <t>DOCUMENTID14</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.27.documentId</t>
+          <t>loanAccount.loanDocuments.13.documentId</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -5389,17 +5389,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME29</t>
+          <t>DOCUMENTNAME15</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.28.document</t>
+          <t>loanAccount.loanDocuments.14.document</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
@@ -5569,21 +5569,21 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER15</t>
+          <t>LOANPARAMETER8</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.15.value</t>
+          <t>loanAccount.loanParameters.8.value</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a financial summary metric used as a key input for underwriting calculations for this specific loan application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A key financial input derived from bureau for underwriting and eligibility calculation for the current loan.</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -5619,16 +5619,16 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER16</t>
+          <t>LOANPARAMETER9</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.16.value</t>
+          <t>loanAccount.loanParameters.9.value</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a credit bureau summary metric used for underwriting and risk assessment of the loan application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A bureau summary metric used for underwriting the loan application.</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5664,16 +5664,16 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER17</t>
+          <t>LOANPARAMETER10</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.17.value</t>
+          <t>loanAccount.loanParameters.10.value</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a credit bureau summary metric used for underwriting and risk assessment of the loan application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A specific bureau summary metric used for underwriting the loan application.</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -5704,17 +5704,17 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER18</t>
+          <t>LOANPARAMETER11</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.18.value</t>
+          <t>loanAccount.loanParameters.11.value</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This field represents a specific fee amount associated with the loan, which is a loan-level charge.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A fee amount specific to the loan product being originated.</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -5749,17 +5749,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER19</t>
+          <t>LOANPARAMETER12</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.19.value</t>
+          <t>loanAccount.loanParameters.12.value</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. UMRN (Unique Mandate Reference Number) is the identifier for the repayment mandate set up for this specific loan.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. An identifier for the loan's repayment mandate, which is an application-level detail.</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -5799,16 +5799,16 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER20</t>
+          <t>LOANPARAMETER13</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.20.value</t>
+          <t>loanAccount.loanParameters.13.value</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a credit bureau summary metric of the applicant's total debt, used for underwriting the current loan.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A bureau summary metric representing total outstanding debt, used for underwriting the loan.</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -5839,21 +5839,21 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER21</t>
+          <t>LOANPARAMETER14</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.21.value</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>0.8</v>
+          <t>loanAccount.loanParameters.14.value</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>0.9</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a specific credit behavior flag from a bureau report, used as a direct input for underwriting rules for this loan application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A key credit bureau performance metric used as a direct input for the underwriting decision on the loan.</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -6019,17 +6019,17 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER22</t>
+          <t>LOANPARAMETER15</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.22.value</t>
+          <t>loanAccount.loanParameters.15.value</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This represents a specific fee or charge associated with the loan.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A fee specific to the loan application.</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM12</t>
+          <t>LOANAPPLICANTPARAM19</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.11.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.18.value</t>
         </is>
       </c>
       <c r="F124" s="4" t="n">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field describes the stability of the applicant's employment, which is part of their personal profile.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes the stability of the applicant's employment, a personal profile attribute.</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -6154,21 +6154,21 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER23</t>
+          <t>LOANPARAMETER16</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.23.value</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>0.8</v>
+          <t>loanAccount.loanParameters.16.value</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>0.9</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a credit behavior metric from a bureau report, used as a key input for underwriting the loan application.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A key credit bureau performance metric used as a direct input for the underwriting decision on the loan.</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM13</t>
+          <t>LOANAPPLICANTPARAM20</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.12.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.19.value</t>
         </is>
       </c>
       <c r="F128" s="4" t="n">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field represents a component of the applicant's office address, part of their employment profile.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Part of the applicant's employment address.</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM14</t>
+          <t>LOANAPPLICANTPARAM21</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.13.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.20.value</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field represents a component of the applicant's office address, part of their employment profile.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Part of the applicant's employment address.</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICANTPARAM15</t>
+          <t>LOANAPPLICANTPARAM22</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.21.value</t>
         </is>
       </c>
       <c r="F130" s="4" t="n">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This field represents a component of the applicant's office address, part of their employment profile.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Part of the applicant's employment address.</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -6424,21 +6424,21 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER24</t>
+          <t>LOANAPPLICANTPARAM23</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.24.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.22.value</t>
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a reference number for the O-KYC verification process performed for this specific loan application.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. An identifier related to the applicant's KYC documentation.</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -6514,21 +6514,21 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER25</t>
+          <t>LOANPARAMETER17</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.25.value</t>
+          <t>loanAccount.loanParameters.17.value</t>
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a summary of the applicant's total outstanding debt, a key financial metric for underwriting the loan.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A bureau summary metric representing total outstanding debt, used for underwriting the loan.</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -6559,17 +6559,17 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER26</t>
+          <t>LOANPARAMETER18</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.26.value</t>
+          <t>loanAccount.loanParameters.18.value</t>
         </is>
       </c>
       <c r="F135" s="4" t="n">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This represents a specific fee or charge associated with the loan origination process.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A fee specific to the loan application process.</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -6694,21 +6694,21 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER27</t>
+          <t>LOANAPPLICANTPARAM24</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.27.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.23.value</t>
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a reference number for the V-KYC verification process performed for this specific loan application.</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. An identifier related to the applicant's KYC process.</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -6784,17 +6784,17 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTID30</t>
+          <t>DOCUMENTID15</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.29.documentId</t>
+          <t>loanAccount.loanDocuments.14.documentId</t>
         </is>
       </c>
       <c r="F140" s="3" t="n">
@@ -6829,21 +6829,21 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER28</t>
+          <t>LOANPARAMETER19</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.28.value</t>
+          <t>loanAccount.loanParameters.19.value</t>
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This indicates a significant negative credit event from a bureau report, used as a critical input for the loan underwriting decision.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A significant credit bureau flag used for underwriting and loan decisioning.</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -6862,47 +6862,47 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>insuranceAmountWithGst</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>FEE</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>FEE6</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.fee6</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>llm_pattern_fee</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>The field 'insuranceAmountWithGst' contains the keyword 'insurance' which indicates it is a type of fee or charge.</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>APi field mapping</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM25</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>The field represents a loan-related attribute for the applicant and no specific key is available.</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -6919,21 +6919,21 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>LOANPARAMETER29</t>
+          <t>LOANPARAMETER20</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.29.value</t>
+          <t>loanAccount.loanParameters.20.value</t>
         </is>
       </c>
       <c r="F143" s="7" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. The field name is too short and ambiguous, but it is unlikely to be a standard applicant profile attribute and is likely a process-specific flag or parameter.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The field name 'as' is too generic and non-descriptive to be confidently mapped, but is treated as a loan-level parameter by default.</t>
         </is>
       </c>
       <c r="I143" s="5" t="inlineStr">
@@ -6964,17 +6964,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>DOCUMENTNAME31</t>
+          <t>DOCUMENTNAME16</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanDocuments.30.document</t>
+          <t>loanAccount.loanDocuments.15.document</t>
         </is>
       </c>
       <c r="F144" s="4" t="n">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>The field name contains the document keyword 'agreement' and 'name' suggesting it is a document file name.</t>
+          <t>The field 'loanAggreementName' clearly refers to the name of a loan agreement document.</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -7008,7 +7008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>werize</t>
+          <t>WERIZE</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-07 14:44:31</t>
+          <t>2026-04-07 15:31:02</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7173,27 +7173,27 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>llm_pattern_document_name</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>llm_pattern_fee</t>
+          <t>llm_pattern_document_name</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>70</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24">
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -7267,165 +7267,93 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>bankStatement1Password</t>
+          <t>loanType</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>bankStatement2Password</t>
+          <t>insuranceAmountWithGst</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>bankStatement3Password</t>
+          <t>as</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>bankStatement4Password</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>bankStatement5Password</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>0.70</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>bankStatement6Password</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>bankStatement7Password</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>loanType</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Mandatory Fields Missing:</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Confidence Distribution:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0.90-1.00</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0.80-0.89</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Mandatory Fields Missing:</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>Confidence Distribution:</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>0.90-1.00</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>0.80-0.89</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>0.70-0.79</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
         <is>
           <t>0.00-0.69</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7440,7 +7368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -7504,7 +7432,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>bankStatement1Password</t>
+          <t>loanType</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -7519,25 +7447,25 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>LOANPARAMETER1</t>
+          <t>APPLICANTCUSTOMERTYPE</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.1.value</t>
+          <t>loanAccount.customer.customerType</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>alias_tier4</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
+          <t>Alias match (tier4): 'loanType' → 'APPLICANTCUSTOMERTYPE' (frequency=1)</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -7549,7 +7477,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>bankStatement2Password</t>
+          <t>insuranceAmountWithGst</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -7559,30 +7487,30 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>LOANPARAMETER2</t>
+          <t>LOANAPPLICANTPARAM25</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.2.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>llm_parameter_bucket</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
+          <t>The field represents a loan-related attribute for the applicant and no specific key is available.</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -7594,7 +7522,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>bankStatement3Password</t>
+          <t>as</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -7604,21 +7532,21 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>LOANPARAMETER3</t>
+          <t>LOANPARAMETER20</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.3.value</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>0.7</v>
+          <t>loanAccount.loanParameters.20.value</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -7627,7 +7555,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The field name 'as' is too generic and non-descriptive to be confidently mapped, but is treated as a loan-level parameter by default.</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -7636,278 +7564,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>bankStatement4Password</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER4</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.4.value</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>llm_parameter_bucket</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>bankStatement5Password</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER5</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.5.value</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>llm_parameter_bucket</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>bankStatement6Password</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER6</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.6.value</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>llm_parameter_bucket</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>bankStatement7Password</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER7</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.7.value</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>llm_parameter_bucket</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. This is a temporary credential required for the underwriting process, not a persistent attribute of the applicant's profile.</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>loanType</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>APPLICANTCUSTOMERTYPE</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.customerType</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'loanType' → 'APPLICANTCUSTOMERTYPE' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>APi field mapping</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER29</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.29.value</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>llm_parameter_bucket</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Parameter bucket classifier chose LOANPARAMETER. The field name is too short and ambiguous, but it is unlikely to be a standard applicant profile attribute and is likely a process-specific flag or parameter.</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I10"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>